--- a/reports/oatside-pg-2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/reports/oatside-pg-2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04 18:12</t>
+          <t>2026-05-04 18:27</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/reports/oatside-pg-2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04 18:27</t>
+          <t>2026-05-05 12:56</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/reports/oatside-pg-2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05 12:56</t>
+          <t>2026-05-05 14:39</t>
         </is>
       </c>
     </row>
